--- a/reports/一级子公司A_现金流量表_2025-11.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-11.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>143754000</v>
+        <v>143914702</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1649466000</v>
+        <v>1648288152</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>2897748</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>33358902</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1458247</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>16659032</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>722951</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>8337336</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>583971</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>6666178</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>433707</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>5000187</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>291731</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3334605</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>217248</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2499047</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>145494</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1667866</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>363181</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>4164148</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>182218</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2095701</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>115822</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1324070</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>368600</v>
+        <v>367068</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4229400</v>
+        <v>4231535</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2619000</v>
+        <v>2631638</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>30051000</v>
+        <v>30041476</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>146741600</v>
+        <v>154325726</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>93120000</v>
+        <v>93022168</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1068480000</v>
+        <v>1067778872</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>967901</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>11120105</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>727876</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>8328364</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>482552</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>5559441</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>364775</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>4165204</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>240916</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>2778735</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>183415</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2094176</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>15229000</v>
+        <v>15161849</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>174741000</v>
+        <v>174704570</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>7760000</v>
+        <v>7786591</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>89040000</v>
+        <v>89077009</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3201000</v>
+        <v>3194323</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>36729000</v>
+        <v>36707722</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>119310000</v>
+        <v>122132366</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>27431600</v>
+        <v>32193360</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>179133</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1980000</v>
+        <v>1979897</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1495468</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>16500000</v>
+        <v>16491971</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>921465</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>10120000</v>
+        <v>10126468</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1674601</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>13977618</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>154000000</v>
+        <v>154113043</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>2006053</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>22000000</v>
+        <v>21985327</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>9958615</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>110000000</v>
+        <v>110058319</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>378551</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>4180000</v>
+        <v>4178518</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14356169</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12681568</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3507322</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>38500000</v>
+        <v>38472269</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5524270</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>60500000</v>
+        <v>60471412</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5472872</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>60500000</v>
+        <v>60516108</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>180889</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1980000</v>
+        <v>1979937</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9212481</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4515522</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>49500000</v>
+        <v>49520851</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4490487</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>49500000</v>
+        <v>49470639</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>720401</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>7920000</v>
+        <v>7925569</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>628387</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>6930000</v>
+        <v>6934842</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>90342</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>990000</v>
+        <v>989422</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5326265</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3886216</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>18601600</v>
+        <v>23398008</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>18601600</v>
+        <v>23398008</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
